--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4960,6 +4960,781 @@
       <c r="G173" t="inlineStr">
         <is>
           <t>done 2026-08-02 19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>147</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PANDO Pet Dryer Room PD65 แพนโด้ เครื่องเป่าขน สำหรับสัตว์เลี้ยง รุ่น PD65 ตู้เป่าขน อัตโนม</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qRzC0bKNG</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mp1zyxmcgm4r44.webp</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>฿9990.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>148</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>พร้อมส่ง MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ (ลดขนร่วง ลดคราบน้ำตา ลดกลิ่นมูลสัตว์) ทานได้ทุกสายพันธุ์</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxMmSnMyM</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mopbxox2cfm73f.webp</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>฿547.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>149</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Dr.Zkin Pet Spray ผลิตภัณฑ์สำหรับสัตว์เลี้ยง บำรุงขน ดับกลิ่น เพิ่มความหอม</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70HY9gQhNc</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mhh7zikraarne4.webp</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>฿210.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>150</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Prowild โปรไวลด์ ซีเล็คเต็ด อาหารสุนัขทุกสายพันธุ์/ทุกช่วงวัย ขนาด 15 kg</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fIJKaWMHK</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0m-mbg6gn8vi82g66.webp</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>฿1590.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>151</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>NaviPet Grooming Vacuum KIT 7 in 1 เครื่องปัตตาเลียนตัดแต่งขนสำหรับสัตว์เลี้ยง และดูดฝุ่น กรูมมิ่งสำหรับดูด</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40e06K2cCJ</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-madx77cb5x8wff.webp</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>฿2590.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>152</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PANDO Second Generation Pet Trolleyแพนโด้ รถเข็นสำหรับสัตว์เลี้ยง เวอร์ชันอัพเกรด</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110OWov8hV</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mp208h070r2883.webp</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>฿3390.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>153</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>navipet Smart Pet Dryer (Thai Version) ตู้เป่า ขนสัตว์เลี้ยง 72ลิตร O ZONE ฆ่าเชื้อได้ ประกันศูนย์ไทย</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pyBTXqfWJ</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mnqj2jpnw45hd8.webp</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>฿7900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>154</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>แนะนำ! สมาร์ทฮาร์ท โกลด์ ฟิตแอนด์เฟิร์ม 7+ อาหารสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ 20 กก.</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pbn350qIc</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mp3d3pouixhqeb.webp</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>฿1480.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>155</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>[สินค้าใหม่] PANDO Pet Hair Trimmer 4 in 1 Pro แพนโด้ ชุดอุปกรณ์ตัดขน เล็มขน สัตว์เลี้ยง รุ่น โปร</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30lSuWWyVO</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mp20bnax2bkd6b.webp</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>฿581.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>156</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับสุนัขโต อายุ 1-6 ปี สูตรเนื้อแกะรมควัน ขนาด 8 กก.</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pbn35XQb1</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mn700alam03s8d.webp</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>฿1359.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>157</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>พร้อมส่ง MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ (ลดขนร่วง ลดคราบน้ำตา ลดกลิ่นมูลสัตว์) ทานได้ทุกสายพันธุ์</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W47vxAxHm</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mopbxox2cfm73f.webp</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>฿547.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>158</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>[Doctor By BREATH CARE] อาหารเสริมทางเดินหายใจสุนัข บรรเทาอาการไอ ฮอนคิง แก้สงสารพยุงบรอนเชียล (30 บีบ)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KmzGMOid3</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134207-822wp-mog5oph3ouml25.webp</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>฿1126.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>159</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>[ ตกกิโลละ 119 บาท l ไซส์กระสอบ 15 กิโล ] petheria อาหารสุนัขแบบเม็ดเกรด SUPER PREMIUM มีให้เลือกทุกช่วงวัย</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70HbfvolrB</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98w-lwv3eh1w2dan86.webp</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>฿1798.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>160</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Dog Days อาหารลูกสุนัข (6 kg) สูตร Puppy &amp; Mommy รสแกะและปลาทูน่า</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110OWujz86</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-modfibxbvymma0.webp</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>฿690.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>161</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Dog Days อาหารสุนัขรสเนื้อแกะ (12 kg) Daily เกรด Holistic สูตรลดขนร่วงโดยเฉพาะ โซเดียมต่ำ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPpf2BSBB</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mp3judrlwkcr9c.webp</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>฿1691.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>162</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Petcho แผ่นรองฉี่ แผ่นรองฉี่สุนัข แผ่นรองซับ สัตว์เลี้ยง ซับได้มาก พลังการดูดซับ 6ชั้น ช่วยฝึกขับถ่าย</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W47w2T99w</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lyelrzpqov41c6.webp</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>฿149.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>163</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>เสื้อน้องหมาลาย เครื่องปรุงรส ผ้าไมโครสีสันสดใสพร้อมส่ง</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pyBTgRAjL</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m96tiq9mlglrc3.webp</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>฿50.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>164</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>NAVIPET Wireless Drinking Fountain V1 น้ำพุไร้สายความจุ2.5ลิตร มีแบตในตัว5000 mAh ประกันศูนย์ไทย1 ปี</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gNY8M5yK7</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mf998jaiwff3bb.webp</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>฿742.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>165</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Pawdy อาหารสุนัขเกรดพรีเมียม สำหรับสุนัขสูงวัย อายุมากกว่า 7 ปี สูตรแกะและปลา ผสมเนื้อจระเข้ ขนาด 1.2 กก.</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LGqV615Un</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mn9tb9drwvszd2.webp</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>฿333.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>166</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Prama อาหารสุนัขพราม่าเกรด Holistic มีให้เลือก 2 สูตร เนื้อแกะ และ ปลาทูน่า ขนาด 15kg</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uywec7H9V</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m2idzdnzkn8k02.webp</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>฿1250.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>167</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Pawdy อาหารสุนัขเกรดพรีเมียม สำหรับสุนัขสูงวัย อายุมากกว่า 7 ปี สูตรแกะและปลา ผสมเนื้อจระเข้ ขนาด 1.2 กก. (2 ถุง)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qD763Stp2</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mkgeybc3sfewa9.webp</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>฿643.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>168</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>PANDO Pet Smart Camera Feeder 4L เครื่องให้อาหารอัตโนมัติขนาด 4 ลิตร พร้อมกล้องวิดีโอ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AUrTqTY04A</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mp20hqahb9xq74.webp</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>฿3790.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>169</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>My Paws น้ำยาล้างจาน น้ำยาล้างของเล่น น้ำยาล้างจานสำหรับสัตว์เลี้ยง สารสกัดจากธรรมชาติ อ่อนโยน สำหรับสัตว์เลี้ยงทุกชนิด</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1Vwf7wPVkj</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mp37aagvwj5te3.webp</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>฿38.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>170</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับสุนัขโต อายุ 1-6 ปี สูตรเนื้อวัวย่างและเห็ดทรัฟเฟิล ขนาด 8 กก. (มี 2 ขนาด)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATZ4DLj5r</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mn6zvfws7coy54.webp</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>฿1278.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>171</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>yoyopet : แปรงกําจัดขนสองด้าน แปรงสางขนเสีย หวีซี่สแตนเลส กำจัดขนลอย ขนปม อุปกรณ์ดูแลขนสัตว์เลี้ยง</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXITJ3q7F</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m4ze403ouvtpc2.webp</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>฿58.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>172</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อวัวและนม 15กก.</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gNY8RukUK</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/9ec893796776a5020ab0abee60620b57.webp</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>฿1030.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>173</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>(คละรสไม่ได้) สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง 400g x24 กระป๋อง(ยกแพ็ค)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KfWSNx5gi</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mlx53j8akmbp86.webp</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>฿1090.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>174</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PANDO Double-Layer Pet Trolley แพนโด้ รถเข็นแบบสองชั้นสำหรับสัตว์เลี้ยง</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40e06ahvjJ</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mj6sg1hg00sj92.webp</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>฿5990.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>175</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>[ขายดี] สมาร์ทฮาร์ท อาหารสุนัข สุนัขโต รสเนื้ออบ 10 กก. / SmartHeart Adult Roast Beef 10kg</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70Hbg6gXva</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-m682zid86p6f5f.webp</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>฿819.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>176</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>[แบรนด์ขายดีอันดับ 1]JerHigh เจอร์ไฮ สติ๊ก ขนมสุนัข ขนาด 60 กรัม จำนวน 12 ซอง (เลือกรสด้านใน)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VDsH33sg7</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0s-mb7mtm884ks64b.webp</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>฿741.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>177</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>กรง สแตนเลส 304 กรงสัตว์เลี้ยงขนาดใหญ่（125*110cm）กรงสแตนเลส กรงสุนัขพับได้ กรงสุนัข คอกกรงสัตว์เลี้ยง dog cages crates</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/qgyKnqQa2</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r992-lya8q6n2fnah9e.webp</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>฿2667.00</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4987,6 +4987,11 @@
           <t>฿9990.00</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>done 2026-09-12 21:23</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -5763,7 +5768,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "E", "D", "C", "H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม"], "last_roles": ["R1", "R4", "R6", "R1", "R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ สมาร์ทฮาร์ท โกลด์ ซีเลกต์ มูสลี่ ราคาแค่ 215 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น KUMAま ห้องน้ำแมว Minimal Design ราคาแค่ 1050 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เสื้อจุดให้สัตว์เลี้ยง เสื้อแมว เสื้อผ้าสัตว์ ราคาแค่ 51 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ใส่โค้ดลดเพิ่ม Petology ทรายแมวภูเขาไฟ เก็บกล ราคาแค่ 510 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224"]}</t>
+          <t>{"last_personas": ["E", "D", "C", "H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง"], "last_styles": ["การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ"], "last_roles": ["R4", "R6", "R1", "R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3"], "recent_captions": ["เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น KUMAま ห้องน้ำแมว Minimal Design ราคาแค่ 1050 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เสื้อจุดให้สัตว์เลี้ยง เสื้อแมว เสื้อผ้าสัตว์ ราคาแค่ 51 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ใส่โค้ดลดเพิ่ม Petology ทรายแมวภูเขาไฟ เก็บกล ราคาแค่ 510 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5017,6 +5017,11 @@
           <t>฿547.00</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>done 2026-09-13 22:03</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5768,7 +5773,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "D", "C", "H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง"], "last_styles": ["การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ"], "last_roles": ["R4", "R6", "R1", "R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3"], "recent_captions": ["เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น KUMAま ห้องน้ำแมว Minimal Design ราคาแค่ 1050 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เสื้อจุดให้สัตว์เลี้ยง เสื้อแมว เสื้อผ้าสัตว์ ราคาแค่ 51 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ใส่โค้ดลดเพิ่ม Petology ทรายแมวภูเขาไฟ เก็บกล ราคาแค่ 510 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
+          <t>{"last_personas": ["D", "C", "H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R6", "R1", "R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เสื้อจุดให้สัตว์เลี้ยง เสื้อแมว เสื้อผ้าสัตว์ ราคาแค่ 51 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ใส่โค้ดลดเพิ่ม Petology ทรายแมวภูเขาไฟ เก็บกล ราคาแค่ 510 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5047,6 +5047,11 @@
           <t>฿210.00</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>done 2026-09-15 00:03</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5773,7 +5778,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "C", "H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R6", "R1", "R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ เสื้อจุดให้สัตว์เลี้ยง เสื้อแมว เสื้อผ้าสัตว์ ราคาแค่ 51 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ใส่โค้ดลดเพิ่ม Petology ทรายแมวภูเขาไฟ เก็บกล ราคาแค่ 510 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
+          <t>{"last_personas": ["C", "H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ"], "last_roles": ["R1", "R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ใส่โค้ดลดเพิ่ม Petology ทรายแมวภูเขาไฟ เก็บกล ราคาแค่ 510 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5077,6 +5077,11 @@
           <t>฿1590.00</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>done 2026-09-15 22:41</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5778,7 +5783,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ"], "last_roles": ["R1", "R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ใส่โค้ดลดเพิ่ม Petology ทรายแมวภูเขาไฟ เก็บกล ราคาแค่ 510 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
+          <t>{"last_personas": ["H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ"], "last_roles": ["R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5107,6 +5107,11 @@
           <t>฿2590.00</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>done 2026-09-16 22:33</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5783,7 +5788,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ"], "last_roles": ["R4", "R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น PANDO Double-Layer Pet Trolley ราคาแค่ 5990 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
+          <t>{"last_personas": ["F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C"], "last_hooks": ["โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง"], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ"], "last_roles": ["R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1"], "recent_captions": ["โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5137,6 +5137,11 @@
           <t>฿3390.00</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>done 2026-09-17 22:40</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -5788,7 +5793,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C"], "last_hooks": ["โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง"], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ"], "last_roles": ["R2", "R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1"], "recent_captions": ["โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คอลลาเจนญี่ปุ่นบำรุงขนและข้อสำหรับสุนัขแมว สู ราคาแค่ 456 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
+          <t>{"last_personas": ["E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B"], "last_hooks": ["ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง"], "last_styles": ["การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ"], "last_roles": ["R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3"], "recent_captions": ["ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5167,6 +5167,11 @@
           <t>฿7900.00</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>done 2026-09-18 22:09</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -5793,7 +5798,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B"], "last_hooks": ["ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง"], "last_styles": ["การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ"], "last_roles": ["R8", "R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3"], "recent_captions": ["ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Doctor By BREATH CARE ราคาแค่ 1126 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
+          <t>{"last_personas": ["F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ"], "last_styles": ["คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ"], "last_roles": ["R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G204"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5770,6 +5770,106 @@
       <c r="F204" t="inlineStr">
         <is>
           <t>฿2667.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>178</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ประสิทธิภาพระดับท็อป กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store พร้อมรับโค้ดส่วนลดและผ่อน 0% SpayLater</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AWCoHKL6C</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztn-msxxsasoiscl48</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>฿48,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>179</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A19 Pro หน้าจอ ProMotion 120Hz แบตเตอรี่อึดยิ่งขึ้น ระบบกล้องโปร เครื่องศูนย์แท้พร้อมประกันศูนย์ไทย</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AsbEphgh5</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztf-msuyb0tv79qff4</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>฿39,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>180</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) จอใหญ่เต็มตา แบตเตอรี่อึดทนทาน รองรับ Apple Intelligence เต็มรูปแบบ ชิป A18 เครื่องศูนย์ไทยแท้</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LnLTzHQeV</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztg-msuy0uk4gkjo7b</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>฿34,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>181</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) พอร์ต USB-C กล้องหลัก 48MP หน้าจอ Dynamic Island คุ้มค่าที่สุดสำหรับรุ่นมาตรฐาน ใช้งานได้ยาวนาน</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fSTPKxXrZ</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://store.storeimages.cdn-apple.com/8756/as-images.apple.com/is/iphone-15-finish-select-202309-6-1inch-black?wid=5120&amp;hei=2880&amp;fmt=p-jpg&amp;qlt=80&amp;.v=1692923777972</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>฿26,900.00</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5779,7 +5779,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ประสิทธิภาพระดับท็อป กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store พร้อมรับโค้ดส่วนลดและผ่อน 0% SpayLater</t>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ร้านค้าทางการ Shopee Mall มั่นใจได้ของแท้ 100% ประกันศูนย์ไทยเต็มปี ไม่เสี่ยงเครื่องย้อมแมว ซื้อของราคาสูงเลือกร้าน Mall อุ่นใจ ปลอดภัยที่สุด</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5870,6 +5870,162 @@
       <c r="F208" t="inlineStr">
         <is>
           <t>฿26,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>182</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Lifinity ชั้นวางจาน ที่คว่ำจาน 120/105ซม ชั้นวางของในครัว ราคา 678.00 บาท</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qc9ZkOEib</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ลด 55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>183</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ ราคา 1955.00 บาท</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4B04MAcB1P</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ลด 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>184</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า ราคา 875.00 บาท</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KiAVfeVSA</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ลด 45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>185</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้ ราคา 634.00 บาท</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VVRwdnTF3</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ลด 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>186</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2 ราคา 14290.00 บาท</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zxrIvShk4</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>ลด 19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>187</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี ราคา 2107.00 บาท</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>ลด 38%</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5797,6 +5797,11 @@
           <t>฿48,900.00</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>done 2026-09-19 21:48</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -5887,7 +5892,6 @@
           <t>https://s.shopee.co.th/1qc9ZkOEib</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
@@ -5913,7 +5917,6 @@
           <t>https://s.shopee.co.th/4B04MAcB1P</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
@@ -5939,7 +5942,6 @@
           <t>https://s.shopee.co.th/9KiAVfeVSA</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
@@ -5965,7 +5967,6 @@
           <t>https://s.shopee.co.th/5VVRwdnTF3</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
@@ -5991,7 +5992,6 @@
           <t>https://s.shopee.co.th/9zxrIvShk4</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
@@ -6017,7 +6017,6 @@
           <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
@@ -6054,7 +6053,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ"], "last_styles": ["คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ"], "last_roles": ["R2", "R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ใส่โค้ดลดเพิ่ม Petology ห้องน้ำแมวอัตโนมัติ ด ราคาแค่ 13900 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"]}</t>
+          <t>{"last_personas": ["B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ"], "last_roles": ["R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5197,6 +5197,11 @@
           <t>฿1480.00</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>done 2026-09-20 21:52</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6053,7 +6058,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ"], "last_roles": ["R5", "R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น โต๊ะวางชามอาหารน้องแมว และ น้องหมา น่ารัก ราคาแค่ 199 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3"], "recent_captions": ["มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5832,6 +5832,11 @@
           <t>฿39,900.00</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>done 2026-09-22 00:12</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -6058,7 +6063,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R7", "R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3"], "recent_captions": ["มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชุดสุดคุ้มFRONTLINE PLUS CAT ผลิตภัณฑ์หยดกำจั ราคาแค่ 982 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง"], "last_styles": ["คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ"], "last_roles": ["R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5227,6 +5227,11 @@
           <t>฿581.00</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>done 2026-09-22 22:43</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6063,7 +6068,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง"], "last_styles": ["คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ"], "last_roles": ["R2", "R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ขนมแมวเลีย มีโอ ขนมแมวเลีย เพอร์เฟคมิกซ์ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง"], "last_styles": ["คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก"], "last_roles": ["R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2"], "recent_captions": ["เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5867,6 +5867,11 @@
           <t>฿34,900.00</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>done 2026-09-23 22:35</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -6068,7 +6073,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง"], "last_styles": ["คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก"], "last_roles": ["R5", "R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2"], "recent_captions": ["เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ของกิน ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น g x VetOLOGY ขนมเลียสำหรับแมวและสุนัข ราคาแค่ 368 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A", "C"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ"], "last_styles": ["การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก", "มุกน้องหมาเบาๆ"], "last_roles": ["R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2", "R3"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนที่เหล่าทาสจะจ่ายเงินซื้อสมาร์ตโฟนราคาสูงต้องตรวจเช็กให้ชัวร์ว่าไม่ใช่เครื่องย้อมแมว น้องตูบเลยพามาดูมือถือ iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ราคา 34,900 บาท จากร้าน Apple Flagship Store ใน Shopee Mall ที่ไว้ใจได้ว่าเป็นเครื่องศูนย์ไทยแท้และมีประกันศูนย์ 1 ปีเต็มฮะ มีทาสคนไหนกำลังเล็ง iPhone 16 Plus สเปกจอใหญ่ แบตอึด ในงบ 34,900 บาทนี้อยู่บ้างโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5257,6 +5257,11 @@
           <t>฿1359.00</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>done 2026-09-24 22:55</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6073,7 +6078,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A", "C"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ"], "last_styles": ["การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก", "มุกน้องหมาเบาๆ"], "last_roles": ["R5", "R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2", "R3"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น I&amp;CATอพาร์ทเมนท์แมว ผ้ากำมะหยี่ ชั้น ลับเล็บ ราคาแค่ 299 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนที่เหล่าทาสจะจ่ายเงินซื้อสมาร์ตโฟนราคาสูงต้องตรวจเช็กให้ชัวร์ว่าไม่ใช่เครื่องย้อมแมว น้องตูบเลยพามาดูมือถือ iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ราคา 34,900 บาท จากร้าน Apple Flagship Store ใน Shopee Mall ที่ไว้ใจได้ว่าเป็นเครื่องศูนย์ไทยแท้และมีประกันศูนย์ 1 ปีเต็มฮะ มีทาสคนไหนกำลังเล็ง iPhone 16 Plus สเปกจอใหญ่ แบตอึด ในงบ 34,900 บาทนี้อยู่บ้างโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A", "C", "A"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2", "R3", "R4"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนที่เหล่าทาสจะจ่ายเงินซื้อสมาร์ตโฟนราคาสูงต้องตรวจเช็กให้ชัวร์ว่าไม่ใช่เครื่องย้อมแมว น้องตูบเลยพามาดูมือถือ iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ราคา 34,900 บาท จากร้าน Apple Flagship Store ใน Shopee Mall ที่ไว้ใจได้ว่าเป็นเครื่องศูนย์ไทยแท้และมีประกันศูนย์ 1 ปีเต็มฮะ มีทาสคนไหนกำลังเล็ง iPhone 16 Plus สเปกจอใหญ่ แบตอึด ในงบ 34,900 บาทนี้อยู่บ้างโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อาหารสุนัข ตัวนี้มีจุดเด่นคือ เกรดโฮลิสติก สำหรับสุนัขโต ราคา 1359 บาทฮะ บ้านไหนเคยใช้ อาหารสุนัข แบบนี้ จุดที่ต้องเช็กก่อนซื้อคืออะไรฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5902,6 +5902,11 @@
           <t>฿26,900.00</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>done 2026-09-25 22:56</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -6078,7 +6083,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A", "C", "A"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R7", "R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2", "R3", "R4"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Cutepol ทรายแมวเต้าหู้ ดับกลิ่นสูงสุด จับตัวก ราคาแค่ 499 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนที่เหล่าทาสจะจ่ายเงินซื้อสมาร์ตโฟนราคาสูงต้องตรวจเช็กให้ชัวร์ว่าไม่ใช่เครื่องย้อมแมว น้องตูบเลยพามาดูมือถือ iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ราคา 34,900 บาท จากร้าน Apple Flagship Store ใน Shopee Mall ที่ไว้ใจได้ว่าเป็นเครื่องศูนย์ไทยแท้และมีประกันศูนย์ 1 ปีเต็มฮะ มีทาสคนไหนกำลังเล็ง iPhone 16 Plus สเปกจอใหญ่ แบตอึด ในงบ 34,900 บาทนี้อยู่บ้างโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อาหารสุนัข ตัวนี้มีจุดเด่นคือ เกรดโฮลิสติก สำหรับสุนัขโต ราคา 1359 บาทฮะ บ้านไหนเคยใช้ อาหารสุนัข แบบนี้ จุดที่ต้องเช็กก่อนซื้อคืออะไรฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A", "C", "A", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ"], "last_roles": ["R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2", "R3", "R4", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนที่เหล่าทาสจะจ่ายเงินซื้อสมาร์ตโฟนราคาสูงต้องตรวจเช็กให้ชัวร์ว่าไม่ใช่เครื่องย้อมแมว น้องตูบเลยพามาดูมือถือ iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ราคา 34,900 บาท จากร้าน Apple Flagship Store ใน Shopee Mall ที่ไว้ใจได้ว่าเป็นเครื่องศูนย์ไทยแท้และมีประกันศูนย์ 1 ปีเต็มฮะ มีทาสคนไหนกำลังเล็ง iPhone 16 Plus สเปกจอใหญ่ แบตอึด ในงบ 34,900 บาทนี้อยู่บ้างโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อาหารสุนัข ตัวนี้มีจุดเด่นคือ เกรดโฮลิสติก สำหรับสุนัขโต ราคา 1359 บาทฮะ บ้านไหนเคยใช้ อาหารสุนัข แบบนี้ จุดที่ต้องเช็กก่อนซื้อคืออะไรฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "การเลือกซื้อมือถือราคาสูงที่มีพอร์ต USB-C อย่าง iPhone 15 ในราคา 26,900 บาท ผ่านร้านค้าทางการ Shopee Mall ถือว่าไว้ใจได้ 100% เพราะได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือเครื่องหิ้วให้ปวดหัวฮะ\n\nแล้วถ้าพาน้องตูบไปวิ่งเล่น พี่ๆ คิดว่ากล้อง 48MP จะถ่ายภาพตอนผมสะบัดขนได้คมชัดระดับไหนฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5287,6 +5287,11 @@
           <t>฿547.00</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>done 2026-09-26 22:06</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6083,7 +6088,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A", "C", "A", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["คำถาม", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ"], "last_roles": ["R3", "R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2", "R3", "R4", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น 🏆Pupping Petmat รุ่น Rug ราคาแค่ 4250 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนที่เหล่าทาสจะจ่ายเงินซื้อสมาร์ตโฟนราคาสูงต้องตรวจเช็กให้ชัวร์ว่าไม่ใช่เครื่องย้อมแมว น้องตูบเลยพามาดูมือถือ iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ราคา 34,900 บาท จากร้าน Apple Flagship Store ใน Shopee Mall ที่ไว้ใจได้ว่าเป็นเครื่องศูนย์ไทยแท้และมีประกันศูนย์ 1 ปีเต็มฮะ มีทาสคนไหนกำลังเล็ง iPhone 16 Plus สเปกจอใหญ่ แบตอึด ในงบ 34,900 บาทนี้อยู่บ้างโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อาหารสุนัข ตัวนี้มีจุดเด่นคือ เกรดโฮลิสติก สำหรับสุนัขโต ราคา 1359 บาทฮะ บ้านไหนเคยใช้ อาหารสุนัข แบบนี้ จุดที่ต้องเช็กก่อนซื้อคืออะไรฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "การเลือกซื้อมือถือราคาสูงที่มีพอร์ต USB-C อย่าง iPhone 15 ในราคา 26,900 บาท ผ่านร้านค้าทางการ Shopee Mall ถือว่าไว้ใจได้ 100% เพราะได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือเครื่องหิ้วให้ปวดหัวฮะ\n\nแล้วถ้าพาน้องตูบไปวิ่งเล่น พี่ๆ คิดว่ากล้อง 48MP จะถ่ายภาพตอนผมสะบัดขนได้คมชัดระดับไหนฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["D", "C", "H", "G", "G", "D", "A", "F", "H", "F", "G", "D", "A", "G", "A", "F", "F", "A", "H", "F", "G", "C", "B", "D", "G", "C", "E", "B", "H", "D", "F", "D", "C", "H", "B", "C", "C", "D", "C", "C", "B", "B", "C", "B", "A", "A", "C", "A", "D", "B"], "last_hooks": ["โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "กำลังหาของแบบนี้อยู่พอดี", "แชร์เผื่อมีคนกำลังหาอยู่", "โดนป้ายยามาอีกที", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "มีใครเป็นเหมือนผมไหม", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง", "เปิดด้วยคำถามเฉพาะถึงบ้านที่เคยใช้จริง", "เปิดด้วยข้อที่ทาสหมาควรตรวจสอบก่อนซื้อ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยปัญหาของคนเลี้ยงหมาที่สินค้าประเภทนี้เกี่ยวข้อง"], "last_styles": ["คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "คำถามเฉพาะ", "ปัญหาและทางเลือก", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ", "มุกน้องหมาเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R7", "R1", "R8", "R3", "R7", "R7", "R8", "R1", "R4", "R3", "R3", "R2", "R1", "R5", "R6", "R4", "R6", "R6", "R4", "R5", "R1", "R7", "R3", "R7", "R5", "R3", "R8", "R6", "R8", "R1", "R3", "R8", "R5", "R6", "R4", "R3", "R4", "R1", "R4", "R1", "R3", "R3", "R1", "R3", "R2", "R2", "R3", "R4", "R3", "R3"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น สมาร์ทฮาร์ท อาหารสุนัข สำหรับลูกสุนัข รสเนื้อ ราคาแค่ 1030 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pawdy อาหารสุนัขเกรดพรีเมียม Holistic สำหรับส ราคาแค่ 1359 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆฮะ ตัวนี้มีจุดเด่นคือ Virbac น้ำยาทำความสะอาดช่องหู อิพิโอติก EpiOt ราคาแค่ 493 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แพ็ค CATE เคท ขนมแมวเลีย ราคาแค่ 639 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ FABLEME —PET BASKET เข่งใส่แมว ราคาแค่ 200 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สินค้าใหม่ PANDO Pet Hair ราคาแค่ 581 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ทรายแมว แคสตี้ Kasty ทรายแมวเต้าหู้ ราคาแค่ 230 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยฮะ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ 😺 สินค้าอยู่ในไทย พร้อมส่ง 🐱 ราคาแค่ 1698 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ คละรสไม่ได้ สมาร์ทฮาร์ท อาหารสุนัขกระป๋อง กระ ราคาแค่ 1090 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Petology ห้องน้ำแมวอัตโนมัติ ดีไซน์ใหญ่ รองรั ราคาแค่ 8800 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น MJ.Kudson อาหารสุนัขพรีเมียมสูตรแกะ ลดขนร่วง  ราคาแค่ 547 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ไม่คิดว่าจะ... ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ PET RECORDกระบะทรายแมวขนาดใหญ่ ขอบสูง ป้องกัน ราคาแค่ 52 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง 🐈🐱Neakasa ห้องน้ำแมวอัตโนมัติ I Smart ราคาแค่ 10499 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชิ้นในแพ็คเกจใหญ่📍 ลูกกลิ้งกำจัดขน เก็บขนและฝ ราคาแค่ 60 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น F&amp;G วิลล่าแมว Cat Villa ราคาแค่ 1999 บาท ดีกว่าเห็นๆ เลยฮะ\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของใช้สัตว์เลี้ยง ตัวนี้มาใช้ได้สักพักแล้วฮะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แถมฝาปิด ส่งฟรี❤️ โอ่งแมวดินเผา16 นิ้ว ราคาแค่ 692 บาท ดีจริง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เมื่อวานเพิ่งเจอ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น คอนโดแมว คอนโดแมวไม้ บ้านแมว เหมาะสำหรับเลี้ย ราคาแค่ 658 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของใช้สัตว์เลี้ยง ดีๆฮะ ตัวนี้มีจุดเด่นคือ Petoya คอลลาเจนญี่ปุ่นบำรุงข้อและขน สำหรับสุน ราคาแค่ 490 บาท เผื่อใครกำลังสนใจอยู่\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของใช้สัตว์เลี้ยงตัวนี้เลยฮะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Dog Days อาหารลูกสุนัข สูตร ราคาแค่ 690 บาท\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ เด็กๆ ที่บ้านชอบกันใหญ่ แย่งกันกินตึม สรรหามานานในที่สุดก็เจอ มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น ยกโหล Nekko อาหารเปียกแมว กรัม12ซอง ราคาแค่ 159 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿159", "โดนป้ายยามาอีกที ตอนแรกผมก็นึกว่า ตะกร้าที่นอนแมว รุ่น Fableme ทรงเข่งมินิมอล ราคา 220 บาทอันนี้ จะกลายเป็นที่เก็บกระดูกของน้องตูบซะแล้วเพราะหน้าตาคล้ายเข่งปลาทูแถวบ้านเหลือเกิน แต่พอสอยมาลอง เจ้านายกลับเข้าไปนอนขดสิงสถิตยาวไม่ยอมลุกเลยโฮ่ง ใครกำลังหา ที่นอนแมวราคาประหยัด ไปแต่งบ้านสวยๆ แชร์ต่อให้เพื่อนที่เจอปัญหาซื้อเตียงแพงแล้วแมวนอนกล่องกระดาษเซฟเก็บไว้ดูเลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿220", "ไม่คิดว่าจะ... เดินเอื่อยๆ ไปสะดุดเจอป้ายลดราคาสเปรย์สัตว์เลี้ยงเหลือแค่ 210 บาทเองฮะ ปกติผมวิ่งซนจนเนื้อตัวซกมกแต่พอพ่นอันนี้เข้าไปก็ช่วยบำรุงขนแถมดับกลิ่นหอมฟุ้งเหมือนหมาคุณหนูขึ้นมาทันทีโฮ่ง บ้านไหนมีตูดหมึกตัวแสบกลิ่นแรงเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันได้นะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿210", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังเจอปัญหาน้องหมาขนร่วงกับคราบน้ำตากวนใจจนปวดหัวแบบผมบ้างฮะ? ผมได้ลองกินอาหารสุนัขรสแกะราคา 542 บาทตัวนี้มาระยะหนึ่ง มันช่วยลดขนร่วงและคราบน้ำตาได้ตรงจุดมากโฮ่ง ใครเลี้ยงสุนัขอยู่แชร์ต่อให้เพื่อนที่เจอปัญหานี้เก็บไว้ดูได้เลยนะฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿542", "เห็นคนพูดถึงเยอะเลยลอง เครื่องแต่งขนสัตว์ รุ่น BM1 เพราะปกติผมสู้ชีวิตกับกองขนว่อนเต็มบ้านจนนึกว่าตัวเองเป็นสุนัขพันทางโฮ่ง ตัวนี้มีฟังก์ชัน 8 in 1 ดูดและเป่าขน พร้อมถังเก็บขนาด 2.5L จัดมาในราคา 5212 บาท ช่วยจัดการขนที่ลอยเข้าปากน้องตูบตอนนอนได้สะใจมากฮะ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ หรือเซฟเก็บไว้ดูตอนช้อปได้เลย\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿5212", "มีใครเป็นเหมือนผมไหม ตอนแรกก็ลังเลไม่แน่ใจว่าพวกห้องน้ำแมวอัตโนมัติจะโอเคไหม แต่สุดท้ายผมก็จัด NOTTY Global เวอร์ชัน Global ราคา 7888 บาทมาลองจนได้ฮะ พอได้ลองใช้จริงแล้วถึงได้รู้ว่าเป็นยังไง ใครที่กำลังหาห้องน้ำแมวอัตโนมัติรุ่นนี้อยู่ แชร์ต่อให้เพื่อนทาสแมวหรือเซฟเก็บไว้ดูได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7888", "อันนี้เกินคาดจริงๆ เมื่อก่อนบ้านผมปวดหัวกับการเลือกซื้ออาหารเปียกแมวให้แมวต่างวัยมาก แต่พอได้ตัวนี้ที่เป็นแบบคละรส ครบทุกช่วงวัย ขนาด 70g (12 ซอง) ชีวิตสบายขึ้นเยอะ แมวกินหมดทุกซองเลยฮะ สินค้าตัวนี้ช่วยเปลี่ยนชีวิตการดูแลแมวในบ้านให้ง่ายขึ้นมากๆ แถมผมบังเอิญไปเจอราคาโปรโมชั่นมาแค่ 265 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลย โฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿265", "เมื่อวานเพิ่งเจอศึกหนักตอนโดนจับอาบน้ำ วิ่งหนีไดร์เป่าผมสะบัดน้ำใส่ทาสจนเปียกซกเหมือนโดนพายุเข้าเลยฮะ แต่ตอนนี้ผมรอดแล้วเพราะมี ตู้เป่าขนสัตว์ รุ่น PD65 ที่มาพร้อมระบบเป่าขนสัตว์เลี้ยงอัตโนมัติ นั่งข้างในชิลๆ จนแห้งสนิท ในราคา 9990 บาท ทาสคนไหนปวดหัวกับการเป่าขนหมาแมวอย่าลืมแชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปกันนะโฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿9990", "ตอนแรกไม่ได้จะซื้อ แต่ผมทนก้มตักอึแมวทุกวัน แถมกลิ่นเหม็นคละคลุ้งอึดอัดไปทั่วบ้านไม่ไหวแล้วฮะ พอได้ห้องน้ำแมวราคา 3,199 บาท เครื่องนี้มาช่วยตักอึอัตโนมัติและช่วยลดกลิ่น ชีวิตน้องตูบสบายขึ้นเยอะเลยโฮ่ง แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿3199", "กำลังหาของแบบนี้อยู่พอดี เวลาจะพาเด็กๆ ในบ้านออกเดินทาง มีใครเคยปวดหัวเรื่องการพาเค้าขึ้นรถบ้างไหมฮะ? ผมไปเจอกล่องเดินทางสัตว์เลี้ยงสำหรับพกพาสัตว์เลี้ยงเดินทาง ในราคา 973 บาท เลยรีบเอามาบอกทุกคนโฮ่ง! ใครที่กำลังวางแผนพาแมวหมาเที่ยว ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿973", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วงนี้เจอปัญหาเจ้านายที่บ้านเมินอาหารเดิมๆ ผมเลยลองหา อาหารเปียกแมว Pramy Gravy สูตรเกรวี่ สำหรับแมว 2 เดือนขึ้นไป มาฮะ ตัวนี้ขนาด 70g ได้ทั้งหมด 12ซอง ราคา 256 บาท เด็กๆ เลียหมดจานเลย เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยโฮ่ง\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿256", "โดนป้ายยามาอีกที ทุกทีหลังอาบน้ำ น้องตูบสะบัดตัวน้ำกระจายเต็มบ้าน แถมผมต้องถือไดร์เป่าขนจนแขนแทบหลุด หูอื้อ หน้ามืด แถมกลัวขนเปียกอับเชื้อโรคอีกโฮ่ง จนมาจบที่ ตู้เป่าขนสัตว์ Navipet Smart ขนาด 72L ราคา 7,900 บาท ที่มีระบบฆ่าเชื้อ OZONE จับเข้าไปนั่งเป่าแห้งสบายใจเฉิบ แชร์ต่อให้เพื่อนที่เจอปัญหานี้ไว้ดูเป็นตัวช่วยได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿7900", "ไม่คิดว่าจะต้องคอยเก็บทรายแมวหกเลอะเทอะเต็มบ้านทุกวันเพราะกระบะทรายอันเก่ามันแคบเกินไปฮะ แต่พอผมเปลี่ยนมาใช้ห้องน้ำแมว Smart Cat BO ขนาดใหญ่ ราคา 1000 บาท แล้วชีวิตดีขึ้นเยอะ ทรายไม่หกออกมาข้างนอกอีกเลยโฮ่ง พอได้ห้องน้ำแมวขนาดใหญ่รุ่นนี้มาช่วยแก้ปัญหาตรงจุด พื้นบ้านก็สะอาดขึ้นทันตา แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูตอนช้อปได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1000", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ตอนแรกน้องตูบกะจะส่องของกินตัวเอง แต่ดันเผลอไปกดเจอโปรโมชั่นขนมแมวเลียราคา 109 บาท ที่เลือกคละรสได้ถึง 11 รสชาติ แถมมีขนาดให้เลือกทั้ง 11/20/25/36 ซอง งานนี้ยอมสละเงินกระปุกไปเอาใจเจ้านายแมวที่บ้านเรียบร้อยโฮ่ง ทาสแมวทั้งหลายเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เลี้ยงแมวด้วยกันได้เลยฮะ\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿109", "เห็นคนพูดถึงเยอะเลยลอง เคยแอบกังวลเรื่องกลิ่นเวลาอยู่ใกล้ชิดคนในบ้านกันไหมฮะ? น้องตูบเลยไปซื้อสเปรย์ระงับกลิ่นที่เป็นสูตรอ่อนโยน มีสารสกัดธรรมชาติมาให้คนที่บ้านได้ลองใช้กันในราคา 169 บาท ลองแชร์ต่อให้คนที่รักหรือเซฟเก็บไว้ดูได้เลยฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿169", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังฮะ ส่วนตัวประทับใจจุดเด่น กรงไก่กลางแจ้ง คอกไก่ บ้านไก่ ขนาดใหญ่พิเศษ ราคาแค่ 1224 บาท คิดว่าไงกันบ้าง\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇\n🔥 โปรโมชั่น: ฿1224", "บ้านไหนเคยพาเด็กๆ เข้าตู้เป่าขนสัตว์ รุ่น PD65 กันบ้างฮะ น้องตูบแวะมาชี้พิกัดตัวที่มีระบบเป่าแห้งอัตโนมัติ ราคา 9990 บาท มาฝากโฮ่ง สำหรับคนที่ใช้อยู่จริง ระบบเป่าแห้งอัตโนมัติของรุ่น PD65 ทำให้ขนแห้งสนิทดีไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนจะเลือกซื้ออาหารให้เจ้าตัวแสบ ทาสหมาควรตรวจดูส่วนผสมที่ช่วยแก้ปัญหาเฉพาะจุดก่อนเสมอ ซึ่งตัวนี้น้องตูบไปส่องมาเป็นอาหารสุนัขรสแกะที่มีจุดเด่นเรื่องลดขนร่วง ลดคราบน้ำตา ราคา 547 บาทฮะ พี่ๆ คิดว่าอาหารสุนัขรสแกะที่ช่วยลดขนร่วงและคราบน้ำตากับราคา 547 บาทนี้เหมาะกับสุนัขที่บ้านไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 210 บาทได้สเปรย์สัตว์เลี้ยงที่มีทั้งฟังก์ชันบำรุงขนและดับกลิ่นในขวดเดียวเลยฮะ พี่ๆ คิดว่าสเปรย์สัตว์เลี้ยงที่ช่วยทั้งบำรุงขนและดับกลิ่นในงบ 210 บาทนี้ ตอบโจทย์การดูแลกลิ่นตัวน้องหมาที่บ้านไหมฮะ? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ผมเห็นว่าตัวนี้สะดวกตรงที่กินได้ทุกสายพันธุ์ทุกวัยเลยฮะ โดยเป็นอาหารสุนัขรุ่นซีเล็คเต็ด ขนาด 15 kg ราคา 1,590 บาท \n\nมีบ้านไหนกำลังเล็งอาหารสุนัขกระสอบ 15 kg ราคา 1,590 บาทที่แชร์กันกินได้ทุกวัยแบบนี้อยู่บ้างฮะ? \n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาตัดขนทีไรเศษขนปลิวว่อนเต็มบ้านจนกวาดเหนื่อยเลยฮะ แต่ผมเจอเครื่องตัดขนสัตว์เลี้ยง รุ่น KIT 7 in 1 ที่ตัดขนพร้อมดูดฝุ่นในตัว 7 in 1 ราคา 2,590 บาท พี่ๆ คิดว่าระบบตัดขนพร้อมดูดฝุ่นในตัวของรุ่นนี้จะช่วยให้ตัดขนสุนัขได้สะดวกขึ้นจริงไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "บ้านไหนพาน้องๆ นั่งรถเข็นสัตว์เลี้ยง รุ่น Gen 2 ที่เป็นเวอร์ชันอัปเกรด ราคา 3390 บาทกันบ้างฮะ? น้องตูบกำลังเทียบข้อมูลอยู่ อยากถามว่าตัวเวอร์ชันอัปเกรดนี้ตอบโจทย์เวลาพาเที่ยวไหม โฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เรื่องขนาดตัวของผมกับความจุตู้คือสิ่งที่ทาสหมาต้องเช็กให้ชัวร์ก่อน ซึ่งตู้เป่าขนสัตว์ navipet Smart Pet Dryer มีขนาด 72 ลิตร พร้อมโอโซนฆ่าเชื้อและประกันศูนย์ไทย ในราคา 7,900 บาทฮะ พี่ๆ บ้านไหนเคยพาน้องหมาเข้าไปนั่งเป่าในตู้ขนาด 72 ลิตรนี้แล้วน้องยังกลับตัวได้สะดวกไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "จ่าย 48,900 บาท แลกกับมือถือชิป A20 Pro น้องตูบดมกลิ่นแล้ววางใจได้เพราะเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็มจาก Shopee Mall ไม่ต้องเสี่ยงเจอเครื่องย้อมแมวฮะ พี่ๆ คิดว่าชิป A20 Pro ใน iPhone 18 Pro Max จะตอบโจทย์คนเน้นเล่นเกมกราฟิกหนักๆ ไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ตอนนี้ผมกำลังดูอาหารสุนัขสูตรสำหรับสุนัขสูงอายุ พันธุ์กลาง-ใหญ่ อย่าง สมาร์ทฮาร์ท โกลด์ 7+ ขนาด 20 กก. ราคา 1480 บาทอยู่ฮะ มีบ้านไหนเคยซื้อรุ่นนี้ให้สุนัขพันธุ์กลางหรือพันธุ์ใหญ่ที่บ้านกินแล้วชอบไหมโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เวลาพ่อแม่หมาเจอปัญหาเครื่องช้าตอนเปิดดูคลิปเจ้าตูบ การซื้อสมาร์ตโฟนราคาสูงผ่านร้านทางการ Shopee Mall ช่วยให้อุ่นใจเรื่องของแท้ ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือโดนโกงฮะ น้องตูบไปเช็กสเปกมา iPhone 17 Pro ให้ชิป A19 Pro พร้อมหน้าจอ ProMotion 120Hz ในราคา 39,900 บาท พี่ๆ คิดว่าสเปกชิป A19 Pro กับจอ ProMotion 120Hz ในราคา 39,900 บาทนี้ตอบโจทย์การใช้งานไหมฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "มีบ้านไหนที่เจอปัญหาตัดแต่งขนน้องหมาลำบากแล้วเคยลองปัตตาเลี่ยนสัตว์เลี้ยง รุ่น 4 in 1 Pro กันบ้างฮะ? น้องตูบเห็นข้อมูลว่าตัวนี้มีหัวตัด 4 in 1 ครบชุด ในราคา 581 บาท อยากถามคนที่เคยใช้ว่าหัวตัดทั้ง 4 แบบสลับใช้งานสะดวกไหมฮะ กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "ก่อนที่เหล่าทาสจะจ่ายเงินซื้อสมาร์ตโฟนราคาสูงต้องตรวจเช็กให้ชัวร์ว่าไม่ใช่เครื่องย้อมแมว น้องตูบเลยพามาดูมือถือ iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ราคา 34,900 บาท จากร้าน Apple Flagship Store ใน Shopee Mall ที่ไว้ใจได้ว่าเป็นเครื่องศูนย์ไทยแท้และมีประกันศูนย์ 1 ปีเต็มฮะ มีทาสคนไหนกำลังเล็ง iPhone 16 Plus สเปกจอใหญ่ แบตอึด ในงบ 34,900 บาทนี้อยู่บ้างโฮ่ง? กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "อาหารสุนัข ตัวนี้มีจุดเด่นคือ เกรดโฮลิสติก สำหรับสุนัขโต ราคา 1359 บาทฮะ บ้านไหนเคยใช้ อาหารสุนัข แบบนี้ จุดที่ต้องเช็กก่อนซื้อคืออะไรฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "การเลือกซื้อมือถือราคาสูงที่มีพอร์ต USB-C อย่าง iPhone 15 ในราคา 26,900 บาท ผ่านร้านค้าทางการ Shopee Mall ถือว่าไว้ใจได้ 100% เพราะได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือเครื่องหิ้วให้ปวดหัวฮะ\n\nแล้วถ้าพาน้องตูบไปวิ่งเล่น พี่ๆ คิดว่ากล้อง 48MP จะถ่ายภาพตอนผมสะบัดขนได้คมชัดระดับไหนฮะ?\n\nกดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇", "เจอปัญหาขนร่วงเต็มบ้านแถมคราบน้ำตาเกรอะกรัง น้องตูบเลยกำลังส่องอาหารสุนัข รสแกะ ราคา 547 บาท ที่ระบุจุดเด่นช่วยลดขนร่วง ลดคราบน้ำตา อยู่ฮะ มีบ้านไหนเคยให้สุนัขกินรสแกะตัวนี้แล้วช่วยลดคราบน้ำตากับปัญหาขนร่วงได้ตามสเปกไหมฮะ โฮ่ง กดลิ้งในคอมเมนต์แรกได้เลยฮะ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5417,6 +5417,11 @@
           <t>฿149.00</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>done 2026-09-27T02:46:25.786448+00:00 live-graphics 102319399434080_1109087842079743</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
